--- a/data/3.meta_data/basic_info/26_06_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/26_06_basic_info.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>missingData</t>
+          <t>include</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>both</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>missingData</t>
+          <t>include</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>both</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
